--- a/factory-twin/data/sample_filled_template.xlsx
+++ b/factory-twin/data/sample_filled_template.xlsx
@@ -2783,7 +2783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2988,90 +2988,110 @@
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
+          <t>이송속도 v_f(m/min, 엣지·샌더·런닝쏘)</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>부품 간격 G(m, 엣지)</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>부품당 통과 횟수(엣지 2~4)</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>리턴컨베이어(Y/N)</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
           <t>소정지 빈도(회/시간)</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>예열/청소 시간(분/일)</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>입력버퍼 x</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>입력버퍼 y</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>출력버퍼 x</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>출력버퍼 y</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>버퍼 용량(배치/대차 수)</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>셋업 시간(분)</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>셋업 트리거(색상/두께/제품)</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>MTBF(시간)</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>MTTR(분)</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>불량률(%)</t>
         </is>
       </c>
-      <c r="AQ2" s="2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>명판사진 파일</t>
         </is>
       </c>
-      <c r="AR2" s="2" t="inlineStr">
+      <c r="AV2" s="2" t="inlineStr">
         <is>
           <t>전체사진 파일</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="inlineStr">
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>HMI 사진</t>
         </is>
       </c>
-      <c r="AT2" s="2" t="inlineStr">
+      <c r="AX2" s="2" t="inlineStr">
         <is>
           <t>PLC/HMI 브랜드</t>
         </is>
       </c>
-      <c r="AU2" s="2" t="inlineStr">
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>네트워크 포트(Y/N)</t>
         </is>
       </c>
-      <c r="AV2" s="2" t="inlineStr">
+      <c r="AZ2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -3144,44 +3164,48 @@
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="n">
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AL3" t="n">
         <v>17</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AM3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AN3" t="n">
         <v>19</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AO3" t="n">
         <v>99</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3254,44 +3278,48 @@
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="n">
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="n">
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AL4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AM4" t="n">
         <v>21.5</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AN4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AK4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL4" t="n">
+      <c r="AO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP4" t="n">
         <v>3</v>
       </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="n">
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
         <v>10</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AS4" t="n">
         <v>25</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>1</v>
       </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3364,44 +3392,48 @@
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="n">
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="n">
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="n">
         <v>18.5</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AL5" t="n">
         <v>20.5</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AM5" t="n">
         <v>25</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AN5" t="n">
         <v>20.5</v>
       </c>
-      <c r="AK5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL5" t="n">
+      <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
         <v>6</v>
       </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="n">
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
         <v>15</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AS5" t="n">
         <v>40</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>0.5</v>
       </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3474,44 +3506,48 @@
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="n">
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
         <v>1</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="n">
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
         <v>28.5</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AL6" t="n">
         <v>29</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AM6" t="n">
         <v>37.5</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AN6" t="n">
         <v>29</v>
       </c>
-      <c r="AK6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL6" t="n">
+      <c r="AO6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP6" t="n">
         <v>8</v>
       </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="n">
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
         <v>8</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AS6" t="n">
         <v>30</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>2</v>
       </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3584,44 +3620,48 @@
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="n">
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="n">
         <v>1</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="n">
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="n">
         <v>28.5</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AL7" t="n">
         <v>22</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AM7" t="n">
         <v>35.5</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AN7" t="n">
         <v>22</v>
       </c>
-      <c r="AK7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL7" t="n">
+      <c r="AO7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" t="n">
         <v>5</v>
       </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="n">
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
         <v>6</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AS7" t="n">
         <v>20</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>3</v>
       </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3694,44 +3734,48 @@
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="n">
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="n">
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="n">
         <v>42</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AL8" t="n">
         <v>28.5</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AM8" t="n">
         <v>48</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AN8" t="n">
         <v>28.5</v>
       </c>
-      <c r="AK8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
         <v>12</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AS8" t="n">
         <v>35</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>1</v>
       </c>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3804,44 +3848,48 @@
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="n">
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="n">
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="n">
         <v>45.5</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AL9" t="n">
         <v>22</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AM9" t="n">
         <v>50.5</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AN9" t="n">
         <v>22</v>
       </c>
-      <c r="AK9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL9" t="n">
+      <c r="AO9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP9" t="n">
         <v>9</v>
       </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
         <v>20</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AS9" t="n">
         <v>15</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>2</v>
       </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3910,44 +3958,48 @@
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="n">
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="n">
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="n">
         <v>53</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AL10" t="n">
         <v>28.5</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AM10" t="n">
         <v>59</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AN10" t="n">
         <v>28.5</v>
       </c>
-      <c r="AK10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL10" t="n">
+      <c r="AO10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP10" t="n">
         <v>10</v>
       </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
         <v>0</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AS10" t="n">
         <v>0</v>
       </c>
-      <c r="AP10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>4</v>
+      </c>
       <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4016,44 +4068,48 @@
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="n">
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="n">
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="n">
         <v>53</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AL11" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AM11" t="n">
         <v>59</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AN11" t="n">
         <v>19.5</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AO11" t="n">
         <v>6</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
       <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4122,44 +4178,48 @@
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="n">
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="n">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="n">
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="n">
         <v>26.5</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AL12" t="n">
         <v>13.8</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AM12" t="n">
         <v>31.5</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AN12" t="n">
         <v>13.8</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AO12" t="n">
         <v>2</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AP12" t="n">
         <v>2</v>
       </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="n">
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
         <v>0</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AS12" t="n">
         <v>0</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4228,44 +4288,48 @@
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="n">
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="n">
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="n">
         <v>32.5</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AL13" t="n">
         <v>13.8</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AM13" t="n">
         <v>37.5</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AN13" t="n">
         <v>13.8</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AO13" t="n">
         <v>2</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AP13" t="n">
         <v>2</v>
       </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="n">
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
         <v>0</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AS13" t="n">
         <v>0</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4334,44 +4398,48 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="n">
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="n">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="n">
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="n">
         <v>38.5</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AL14" t="n">
         <v>13.8</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AM14" t="n">
         <v>43.5</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AN14" t="n">
         <v>13.8</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AO14" t="n">
         <v>2</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AP14" t="n">
         <v>2</v>
       </c>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="n">
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
         <v>0</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AS14" t="n">
         <v>0</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4440,44 +4508,48 @@
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="n">
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="n">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="n">
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="n">
         <v>26.5</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AL15" t="n">
         <v>6.8</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AM15" t="n">
         <v>31.5</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AN15" t="n">
         <v>6.8</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AO15" t="n">
         <v>2</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AP15" t="n">
         <v>2</v>
       </c>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="n">
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
         <v>0</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AS15" t="n">
         <v>0</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
       <c r="AU15" t="inlineStr"/>
       <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4546,44 +4618,48 @@
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="n">
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="n">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="n">
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="n">
         <v>32.5</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AL16" t="n">
         <v>6.8</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AM16" t="n">
         <v>37.5</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AN16" t="n">
         <v>6.8</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AO16" t="n">
         <v>2</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AP16" t="n">
         <v>2</v>
       </c>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="n">
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="n">
         <v>0</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AS16" t="n">
         <v>0</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
       <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4652,44 +4728,48 @@
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="n">
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="n">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="n">
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="n">
         <v>38.5</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AL17" t="n">
         <v>6.8</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AM17" t="n">
         <v>43.5</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AN17" t="n">
         <v>6.8</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AO17" t="n">
         <v>2</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AP17" t="n">
         <v>2</v>
       </c>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="n">
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
         <v>0</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AS17" t="n">
         <v>0</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
       <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4758,44 +4838,48 @@
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="n">
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="n">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="n">
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="n">
         <v>47.5</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AL18" t="n">
         <v>13.8</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AM18" t="n">
         <v>52.5</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AN18" t="n">
         <v>13.8</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AO18" t="n">
         <v>3</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
       </c>
       <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
       <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4864,44 +4948,48 @@
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="n">
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="n">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="n">
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="n">
         <v>47.5</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AL19" t="n">
         <v>6.8</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AM19" t="n">
         <v>52.5</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AN19" t="n">
         <v>6.8</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AO19" t="n">
         <v>3</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
       </c>
       <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
       <c r="AU19" t="inlineStr"/>
       <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4970,44 +5058,48 @@
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="n">
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="n">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="n">
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="n">
         <v>55.5</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AL20" t="n">
         <v>16.8</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AM20" t="n">
         <v>55.5</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AN20" t="n">
         <v>16.8</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AO20" t="n">
         <v>99</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
       </c>
       <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
       <c r="AU20" t="inlineStr"/>
       <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/factory-twin/data/sample_filled_template.xlsx
+++ b/factory-twin/data/sample_filled_template.xlsx
@@ -30,6 +30,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_from-to" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_REL관계도" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_운반_출하대장" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_카메라보정" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2777,6 +2778,139 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>카메라당 바닥 제어점 8~12개(근·중·원거리, 겹침 구역 포함, 레이저 측정) + 검증 보행(L자 경로, 보통/대차 속도, 지게차 루프). 홀드아웃 RMS 근 &lt;0.15 m, 원 &lt;0.4 m. 카메라를 건드리면 재보정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>카메라ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>설치 위치 x</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>높이(m)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>하향각(도)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>렌즈(mm)/화각</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>제어점#</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>제어점 바닥 x</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>제어점 바닥 y</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>이미지 u(px)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>이미지 v(px)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>검증보행 구간</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>실측 거리(m)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>추적 거리(m)</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>실측 속도(m/s)</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>추적 속도(m/s)</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>P90 오차(m)</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/factory-twin/data/sample_filled_template.xlsx
+++ b/factory-twin/data/sample_filled_template.xlsx
@@ -5724,12 +5724,14 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>100</v>
       </c>
@@ -5767,12 +5769,14 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>100</v>
       </c>
@@ -5810,12 +5814,14 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>100</v>
       </c>
@@ -5849,12 +5855,14 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>100</v>
       </c>
@@ -5888,12 +5896,14 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>100</v>
       </c>
@@ -5927,12 +5937,14 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>100</v>
       </c>
@@ -5966,12 +5978,14 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>100</v>
       </c>
@@ -6005,12 +6019,14 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>100</v>
       </c>
@@ -6044,12 +6060,14 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>100</v>
       </c>
@@ -6083,12 +6101,14 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>100</v>
       </c>
@@ -6122,12 +6142,14 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>100</v>
       </c>
@@ -6161,12 +6183,14 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>100</v>
       </c>
@@ -6200,12 +6224,14 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>100</v>
       </c>
@@ -6239,12 +6265,14 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>100</v>
       </c>
@@ -6278,12 +6306,14 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>100</v>
       </c>
@@ -6317,12 +6347,14 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>100</v>
       </c>
@@ -6356,12 +6388,14 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>100</v>
       </c>
@@ -6395,12 +6429,14 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>100</v>
       </c>
@@ -6434,12 +6470,14 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>30</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>100</v>
       </c>
@@ -6473,12 +6511,14 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>100</v>
       </c>
@@ -6512,12 +6552,14 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>100</v>
       </c>
@@ -6551,12 +6593,14 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>100</v>
       </c>
@@ -6590,12 +6634,14 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>100</v>
       </c>
@@ -6629,12 +6675,14 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
+      <c r="K26" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
         <v>100</v>
       </c>
@@ -6668,12 +6716,14 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>100</v>
       </c>
@@ -6711,12 +6761,14 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
         <v>100</v>
       </c>
@@ -6754,12 +6806,14 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
+      <c r="K29" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>100</v>
       </c>
@@ -6793,12 +6847,14 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
+      <c r="K30" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>100</v>
       </c>
@@ -6832,12 +6888,14 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
+      <c r="K31" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
         <v>100</v>
       </c>
@@ -6871,12 +6929,14 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
+      <c r="K32" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
         <v>100</v>
       </c>
@@ -6910,12 +6970,14 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
+      <c r="K33" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>100</v>
       </c>
@@ -6949,12 +7011,14 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>100</v>
       </c>
@@ -6988,12 +7052,14 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
+      <c r="K35" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>100</v>
       </c>
@@ -7027,12 +7093,14 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
+      <c r="K36" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>100</v>
       </c>
@@ -7066,12 +7134,14 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
+      <c r="K37" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
         <v>100</v>
       </c>
@@ -7105,12 +7175,14 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
+      <c r="K38" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>100</v>
       </c>
@@ -7144,12 +7216,14 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
+      <c r="K39" t="n">
+        <v>33</v>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>100</v>
       </c>
@@ -7183,12 +7257,14 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
+      <c r="K40" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>100</v>
       </c>
@@ -7222,12 +7298,14 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
+      <c r="K41" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>100</v>
       </c>
@@ -7261,12 +7339,14 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
+      <c r="K42" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>100</v>
       </c>
@@ -7300,12 +7380,14 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
+      <c r="K43" t="n">
+        <v>46</v>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>100</v>
       </c>
@@ -7339,12 +7421,14 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
+      <c r="K44" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>100</v>
       </c>
@@ -7378,12 +7462,14 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
+      <c r="K45" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>100</v>
       </c>
@@ -7417,12 +7503,14 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
+      <c r="K46" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>100</v>
       </c>
@@ -7456,12 +7544,14 @@
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
+      <c r="K47" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>100</v>
       </c>
@@ -7495,12 +7585,14 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
+      <c r="K48" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>100</v>
       </c>
@@ -7534,12 +7626,14 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
+      <c r="K49" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
         <v>100</v>
       </c>
@@ -7573,12 +7667,14 @@
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
+      <c r="K50" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>100</v>
       </c>
@@ -7614,12 +7710,14 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
+      <c r="K51" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>100</v>
       </c>
@@ -7659,12 +7757,14 @@
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
+      <c r="K52" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
         <v>100</v>
       </c>
@@ -7704,12 +7804,14 @@
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
+      <c r="K53" t="n">
+        <v>37</v>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
         <v>100</v>
       </c>
@@ -7745,12 +7847,14 @@
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
+      <c r="K54" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
         <v>100</v>
       </c>
@@ -7786,12 +7890,14 @@
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
+      <c r="K55" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
         <v>100</v>
       </c>
@@ -7827,12 +7933,14 @@
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
+      <c r="K56" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>100</v>
       </c>
@@ -7868,12 +7976,14 @@
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
+      <c r="K57" t="n">
+        <v>35</v>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
         <v>100</v>
       </c>
@@ -7909,12 +8019,14 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
+      <c r="K58" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
         <v>100</v>
       </c>
@@ -7950,12 +8062,14 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
+      <c r="K59" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>100</v>
       </c>
@@ -7991,12 +8105,14 @@
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
+      <c r="K60" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
         <v>100</v>
       </c>
@@ -8032,12 +8148,14 @@
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
+      <c r="K61" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>100</v>
       </c>
@@ -8073,12 +8191,14 @@
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
+      <c r="K62" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
         <v>100</v>
       </c>
@@ -8114,12 +8234,14 @@
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
+      <c r="K63" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
         <v>100</v>
       </c>
@@ -8155,12 +8277,14 @@
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
+      <c r="K64" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
         <v>100</v>
       </c>
@@ -8196,12 +8320,14 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
+      <c r="K65" t="n">
+        <v>38</v>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
         <v>100</v>
       </c>
@@ -8237,12 +8363,14 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
+      <c r="K66" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
         <v>100</v>
       </c>
@@ -8278,12 +8406,14 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
+      <c r="K67" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
         <v>100</v>
       </c>
@@ -8319,12 +8449,14 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
+      <c r="K68" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
         <v>100</v>
       </c>
@@ -8360,12 +8492,14 @@
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
+      <c r="K69" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
         <v>100</v>
       </c>
@@ -8401,12 +8535,14 @@
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
+      <c r="K70" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
         <v>100</v>
       </c>
@@ -8442,12 +8578,14 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
+      <c r="K71" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
         <v>100</v>
       </c>
@@ -8483,12 +8621,14 @@
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
+      <c r="K72" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
         <v>100</v>
       </c>
@@ -8524,12 +8664,14 @@
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
+      <c r="K73" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>100</v>
       </c>
@@ -8565,12 +8707,14 @@
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
+      <c r="K74" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
         <v>100</v>
       </c>
@@ -8606,12 +8750,14 @@
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
+      <c r="K75" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
         <v>100</v>
       </c>
@@ -8651,12 +8797,14 @@
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
+      <c r="K76" t="n">
+        <v>22</v>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
         <v>100</v>
       </c>
@@ -8696,12 +8844,14 @@
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
+      <c r="K77" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
         <v>100</v>
       </c>
@@ -8737,12 +8887,14 @@
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
+      <c r="K78" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
         <v>100</v>
       </c>
@@ -8778,12 +8930,14 @@
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
+      <c r="K79" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
         <v>100</v>
       </c>
@@ -8819,12 +8973,14 @@
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
+      <c r="K80" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
         <v>100</v>
       </c>
@@ -8860,12 +9016,14 @@
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
+      <c r="K81" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
         <v>100</v>
       </c>
@@ -8901,12 +9059,14 @@
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
+      <c r="K82" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
         <v>100</v>
       </c>
@@ -8942,12 +9102,14 @@
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
+      <c r="K83" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>100</v>
       </c>
@@ -8983,12 +9145,14 @@
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
+      <c r="K84" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
         <v>100</v>
       </c>
@@ -9024,12 +9188,14 @@
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
+      <c r="K85" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
         <v>100</v>
       </c>
@@ -9065,12 +9231,14 @@
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
+      <c r="K86" t="n">
+        <v>31</v>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
         <v>100</v>
       </c>
@@ -9106,12 +9274,14 @@
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
+      <c r="K87" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
         <v>100</v>
       </c>
@@ -9147,12 +9317,14 @@
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
+      <c r="K88" t="n">
+        <v>7</v>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
         <v>100</v>
       </c>
@@ -9188,12 +9360,14 @@
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
+      <c r="K89" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
         <v>100</v>
       </c>
@@ -9229,12 +9403,14 @@
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
+      <c r="K90" t="n">
+        <v>9</v>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="n">
         <v>100</v>
       </c>
@@ -9270,12 +9446,14 @@
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
+      <c r="K91" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
       <c r="M91" t="n">
         <v>100</v>
       </c>
@@ -9311,12 +9489,14 @@
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
+      <c r="K92" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
         <v>100</v>
       </c>
@@ -9352,12 +9532,14 @@
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
+      <c r="K93" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="n">
         <v>100</v>
       </c>
@@ -9393,12 +9575,14 @@
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
+      <c r="K94" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="n">
         <v>100</v>
       </c>
@@ -9434,12 +9618,14 @@
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
+      <c r="K95" t="n">
+        <v>16</v>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="n">
         <v>100</v>
       </c>
@@ -9475,12 +9661,14 @@
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
+      <c r="K96" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="n">
         <v>100</v>
       </c>
@@ -9516,12 +9704,14 @@
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
+      <c r="K97" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
       <c r="M97" t="n">
         <v>100</v>
       </c>
@@ -9557,12 +9747,14 @@
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
+      <c r="K98" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
         <v>100</v>
       </c>
@@ -9596,12 +9788,14 @@
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
+      <c r="K99" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
       <c r="M99" t="n">
         <v>100</v>
       </c>
@@ -9639,12 +9833,14 @@
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
+      <c r="K100" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
       <c r="M100" t="n">
         <v>100</v>
       </c>
@@ -9682,12 +9878,14 @@
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
+      <c r="K101" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
         <v>100</v>
       </c>
@@ -9721,12 +9919,14 @@
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
+      <c r="K102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
         <v>100</v>
       </c>
@@ -9760,12 +9960,14 @@
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
+      <c r="K103" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
         <v>100</v>
       </c>
@@ -9799,12 +10001,14 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
+      <c r="K104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="n">
         <v>100</v>
       </c>
@@ -9838,12 +10042,14 @@
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
+      <c r="K105" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
         <v>100</v>
       </c>
@@ -9877,12 +10083,14 @@
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
+      <c r="K106" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
       <c r="M106" t="n">
         <v>100</v>
       </c>
@@ -9916,12 +10124,14 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
+      <c r="K107" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
         <v>100</v>
       </c>
@@ -9955,12 +10165,14 @@
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
+      <c r="K108" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
       <c r="M108" t="n">
         <v>100</v>
       </c>
@@ -9994,12 +10206,14 @@
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
+      <c r="K109" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
         <v>100</v>
       </c>
@@ -10033,12 +10247,14 @@
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
+      <c r="K110" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
       <c r="M110" t="n">
         <v>100</v>
       </c>
@@ -10072,12 +10288,14 @@
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
+      <c r="K111" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
         <v>100</v>
       </c>
@@ -10111,12 +10329,14 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
+      <c r="K112" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
       <c r="M112" t="n">
         <v>100</v>
       </c>
@@ -10150,12 +10370,14 @@
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
+      <c r="K113" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
         <v>100</v>
       </c>
@@ -10189,12 +10411,14 @@
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
+      <c r="K114" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
         <v>100</v>
       </c>
@@ -10228,12 +10452,14 @@
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
+      <c r="K115" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
         <v>100</v>
       </c>
@@ -10267,12 +10493,14 @@
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
+      <c r="K116" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
       <c r="M116" t="n">
         <v>100</v>
       </c>
@@ -10306,12 +10534,14 @@
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
+      <c r="K117" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
         <v>100</v>
       </c>
@@ -10345,12 +10575,14 @@
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
+      <c r="K118" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
       <c r="M118" t="n">
         <v>100</v>
       </c>
@@ -10384,12 +10616,14 @@
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
+      <c r="K119" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
       <c r="M119" t="n">
         <v>100</v>
       </c>
@@ -10423,12 +10657,14 @@
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
+      <c r="K120" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L120" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
       <c r="M120" t="n">
         <v>100</v>
       </c>
@@ -10462,12 +10698,14 @@
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
+      <c r="K121" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="L121" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
       <c r="M121" t="n">
         <v>100</v>
       </c>
@@ -10501,12 +10739,14 @@
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
+      <c r="K122" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L122" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
       <c r="M122" t="n">
         <v>100</v>
       </c>
@@ -10540,12 +10780,14 @@
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
+      <c r="K123" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="L123" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
         <v>100</v>
       </c>
@@ -10583,12 +10825,14 @@
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr">
+      <c r="K124" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L124" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
       <c r="M124" t="n">
         <v>100</v>
       </c>
@@ -10626,12 +10870,14 @@
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
+      <c r="K125" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="L125" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
         <v>100</v>
       </c>
@@ -10665,12 +10911,14 @@
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
+      <c r="K126" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="L126" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
       <c r="M126" t="n">
         <v>100</v>
       </c>
@@ -10704,12 +10952,14 @@
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
+      <c r="K127" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L127" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
       <c r="M127" t="n">
         <v>100</v>
       </c>
@@ -10743,12 +10993,14 @@
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
+      <c r="K128" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
       <c r="M128" t="n">
         <v>100</v>
       </c>
@@ -10782,12 +11034,14 @@
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
+      <c r="K129" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="L129" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
       <c r="M129" t="n">
         <v>100</v>
       </c>
@@ -10821,12 +11075,14 @@
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
+      <c r="K130" t="n">
+        <v>13</v>
+      </c>
+      <c r="L130" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
       <c r="M130" t="n">
         <v>100</v>
       </c>
@@ -10860,12 +11116,14 @@
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
+      <c r="K131" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="L131" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
       <c r="M131" t="n">
         <v>100</v>
       </c>
@@ -10899,12 +11157,14 @@
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
+      <c r="K132" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="L132" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
       <c r="M132" t="n">
         <v>100</v>
       </c>
@@ -10938,12 +11198,14 @@
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
+      <c r="K133" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="L133" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
       <c r="M133" t="n">
         <v>100</v>
       </c>
@@ -10977,12 +11239,14 @@
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr">
+      <c r="K134" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L134" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
       <c r="M134" t="n">
         <v>100</v>
       </c>
@@ -11016,12 +11280,14 @@
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
+      <c r="K135" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="L135" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
       <c r="M135" t="n">
         <v>100</v>
       </c>
@@ -11055,12 +11321,14 @@
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr">
+      <c r="K136" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L136" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
       <c r="M136" t="n">
         <v>100</v>
       </c>
@@ -11094,12 +11362,14 @@
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
+      <c r="K137" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="L137" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
       <c r="M137" t="n">
         <v>100</v>
       </c>
@@ -11133,12 +11403,14 @@
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr">
+      <c r="K138" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="L138" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
       <c r="M138" t="n">
         <v>100</v>
       </c>
@@ -11172,12 +11444,14 @@
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
+      <c r="K139" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="L139" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
       <c r="M139" t="n">
         <v>100</v>
       </c>
@@ -11211,12 +11485,14 @@
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr">
+      <c r="K140" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="L140" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
       <c r="M140" t="n">
         <v>100</v>
       </c>
@@ -11250,12 +11526,14 @@
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr">
+      <c r="K141" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="L141" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
       <c r="M141" t="n">
         <v>100</v>
       </c>
@@ -11289,12 +11567,14 @@
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr">
+      <c r="K142" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L142" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
       <c r="M142" t="n">
         <v>100</v>
       </c>
@@ -11328,12 +11608,14 @@
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
+      <c r="K143" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L143" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
       <c r="M143" t="n">
         <v>100</v>
       </c>
@@ -11367,12 +11649,14 @@
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
+      <c r="K144" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L144" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
         <v>100</v>
       </c>
@@ -11406,12 +11690,14 @@
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
+      <c r="K145" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="L145" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
       <c r="M145" t="n">
         <v>100</v>
       </c>
@@ -11445,12 +11731,14 @@
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr">
+      <c r="K146" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="L146" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
       <c r="M146" t="n">
         <v>100</v>
       </c>
@@ -11484,12 +11772,14 @@
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr">
+      <c r="K147" t="n">
+        <v>36</v>
+      </c>
+      <c r="L147" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
       <c r="M147" t="n">
         <v>100</v>
       </c>
@@ -11527,12 +11817,14 @@
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr">
+      <c r="K148" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="L148" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
       <c r="M148" t="n">
         <v>100</v>
       </c>
@@ -11570,12 +11862,14 @@
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr">
+      <c r="K149" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="L149" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
       <c r="M149" t="n">
         <v>100</v>
       </c>
@@ -11609,12 +11903,14 @@
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr">
+      <c r="K150" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L150" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
       <c r="M150" t="n">
         <v>100</v>
       </c>
@@ -11648,12 +11944,14 @@
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
+      <c r="K151" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="L151" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
       <c r="M151" t="n">
         <v>100</v>
       </c>
@@ -11687,12 +11985,14 @@
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr">
+      <c r="K152" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="L152" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
       <c r="M152" t="n">
         <v>100</v>
       </c>
@@ -11726,12 +12026,14 @@
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
+      <c r="K153" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="L153" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr"/>
       <c r="M153" t="n">
         <v>100</v>
       </c>
@@ -11765,12 +12067,14 @@
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
+      <c r="K154" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L154" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr"/>
       <c r="M154" t="n">
         <v>100</v>
       </c>
@@ -11804,12 +12108,14 @@
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr">
+      <c r="K155" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="L155" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr"/>
       <c r="M155" t="n">
         <v>100</v>
       </c>
@@ -11843,12 +12149,14 @@
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr">
+      <c r="K156" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L156" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr"/>
       <c r="M156" t="n">
         <v>100</v>
       </c>
@@ -11882,12 +12190,14 @@
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr">
+      <c r="K157" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="L157" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
       <c r="M157" t="n">
         <v>100</v>
       </c>
@@ -11921,12 +12231,14 @@
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr">
+      <c r="K158" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L158" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr"/>
       <c r="M158" t="n">
         <v>100</v>
       </c>
@@ -11960,12 +12272,14 @@
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr">
+      <c r="K159" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="L159" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr"/>
       <c r="M159" t="n">
         <v>100</v>
       </c>
@@ -11999,12 +12313,14 @@
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
+      <c r="K160" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L160" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
       <c r="M160" t="n">
         <v>100</v>
       </c>
@@ -12038,12 +12354,14 @@
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr">
+      <c r="K161" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="L161" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr"/>
       <c r="M161" t="n">
         <v>100</v>
       </c>
@@ -12077,12 +12395,14 @@
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr">
+      <c r="K162" t="n">
+        <v>19</v>
+      </c>
+      <c r="L162" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr"/>
       <c r="M162" t="n">
         <v>100</v>
       </c>
@@ -12116,12 +12436,14 @@
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr">
+      <c r="K163" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="L163" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="n">
         <v>100</v>
       </c>
@@ -12155,12 +12477,14 @@
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr">
+      <c r="K164" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L164" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr"/>
       <c r="M164" t="n">
         <v>100</v>
       </c>
@@ -12194,12 +12518,14 @@
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr">
+      <c r="K165" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="L165" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr"/>
       <c r="M165" t="n">
         <v>100</v>
       </c>
@@ -12233,12 +12559,14 @@
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr">
+      <c r="K166" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L166" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr"/>
       <c r="M166" t="n">
         <v>100</v>
       </c>
@@ -12272,12 +12600,14 @@
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr">
+      <c r="K167" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L167" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr"/>
       <c r="M167" t="n">
         <v>100</v>
       </c>
@@ -12311,12 +12641,14 @@
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
+      <c r="K168" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="L168" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
       <c r="M168" t="n">
         <v>100</v>
       </c>
@@ -12350,12 +12682,14 @@
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr">
+      <c r="K169" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L169" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
       <c r="M169" t="n">
         <v>100</v>
       </c>
@@ -12389,12 +12723,14 @@
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
+      <c r="K170" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L170" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr"/>
       <c r="M170" t="n">
         <v>100</v>
       </c>
@@ -12428,12 +12764,14 @@
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
+      <c r="K171" t="n">
+        <v>421.5</v>
+      </c>
+      <c r="L171" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr"/>
       <c r="M171" t="n">
         <v>100</v>
       </c>
@@ -12471,12 +12809,14 @@
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr">
+      <c r="K172" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="L172" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr"/>
       <c r="M172" t="n">
         <v>100</v>
       </c>
@@ -12514,12 +12854,14 @@
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr">
+      <c r="K173" t="n">
+        <v>831.1</v>
+      </c>
+      <c r="L173" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr"/>
       <c r="M173" t="n">
         <v>100</v>
       </c>
@@ -12553,12 +12895,14 @@
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
+      <c r="K174" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="L174" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
       <c r="M174" t="n">
         <v>100</v>
       </c>
@@ -12592,12 +12936,14 @@
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr">
+      <c r="K175" t="n">
+        <v>783.1</v>
+      </c>
+      <c r="L175" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr"/>
       <c r="M175" t="n">
         <v>100</v>
       </c>
@@ -12631,12 +12977,14 @@
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr">
+      <c r="K176" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="L176" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
       <c r="M176" t="n">
         <v>100</v>
       </c>
@@ -12670,12 +13018,14 @@
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr">
+      <c r="K177" t="n">
+        <v>734.7</v>
+      </c>
+      <c r="L177" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr"/>
       <c r="M177" t="n">
         <v>100</v>
       </c>
@@ -12709,12 +13059,14 @@
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr">
+      <c r="K178" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="L178" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr"/>
       <c r="M178" t="n">
         <v>100</v>
       </c>
@@ -12748,12 +13100,14 @@
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr">
+      <c r="K179" t="n">
+        <v>845.2</v>
+      </c>
+      <c r="L179" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr"/>
       <c r="M179" t="n">
         <v>100</v>
       </c>
@@ -12787,12 +13141,14 @@
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr">
+      <c r="K180" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="L180" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr"/>
       <c r="M180" t="n">
         <v>100</v>
       </c>
@@ -12826,12 +13182,14 @@
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr">
+      <c r="K181" t="n">
+        <v>709.4</v>
+      </c>
+      <c r="L181" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
       <c r="M181" t="n">
         <v>100</v>
       </c>
@@ -12865,12 +13223,14 @@
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr">
+      <c r="K182" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="L182" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr"/>
       <c r="M182" t="n">
         <v>100</v>
       </c>
@@ -12904,12 +13264,14 @@
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr">
+      <c r="K183" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="L183" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr"/>
       <c r="M183" t="n">
         <v>100</v>
       </c>
@@ -12943,12 +13305,14 @@
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr">
+      <c r="K184" t="n">
+        <v>160.7</v>
+      </c>
+      <c r="L184" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr"/>
       <c r="M184" t="n">
         <v>100</v>
       </c>
@@ -12982,12 +13346,14 @@
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr">
+      <c r="K185" t="n">
+        <v>726.8</v>
+      </c>
+      <c r="L185" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr"/>
       <c r="M185" t="n">
         <v>100</v>
       </c>
@@ -13021,12 +13387,14 @@
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr">
+      <c r="K186" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="L186" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr"/>
       <c r="M186" t="n">
         <v>100</v>
       </c>
@@ -13060,12 +13428,14 @@
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr">
+      <c r="K187" t="n">
+        <v>286.3</v>
+      </c>
+      <c r="L187" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr"/>
       <c r="M187" t="n">
         <v>100</v>
       </c>
@@ -13099,12 +13469,14 @@
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr">
+      <c r="K188" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="L188" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr"/>
       <c r="M188" t="n">
         <v>100</v>
       </c>
@@ -13138,12 +13510,14 @@
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr">
+      <c r="K189" t="n">
+        <v>595.8</v>
+      </c>
+      <c r="L189" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr"/>
       <c r="M189" t="n">
         <v>100</v>
       </c>
@@ -13177,12 +13551,14 @@
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr">
+      <c r="K190" t="n">
+        <v>198</v>
+      </c>
+      <c r="L190" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr"/>
       <c r="M190" t="n">
         <v>100</v>
       </c>
@@ -13216,12 +13592,14 @@
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr">
+      <c r="K191" t="n">
+        <v>483.5</v>
+      </c>
+      <c r="L191" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr"/>
       <c r="M191" t="n">
         <v>100</v>
       </c>
@@ -13255,12 +13633,14 @@
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr">
+      <c r="K192" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="L192" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr"/>
       <c r="M192" t="n">
         <v>100</v>
       </c>
@@ -13294,12 +13674,14 @@
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr">
+      <c r="K193" t="n">
+        <v>278.5</v>
+      </c>
+      <c r="L193" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr"/>
       <c r="M193" t="n">
         <v>100</v>
       </c>
@@ -13333,12 +13715,14 @@
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr">
+      <c r="K194" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="L194" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr"/>
       <c r="M194" t="n">
         <v>100</v>
       </c>
@@ -13372,12 +13756,14 @@
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr">
+      <c r="K195" t="n">
+        <v>302.6</v>
+      </c>
+      <c r="L195" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr"/>
       <c r="M195" t="n">
         <v>100</v>
       </c>
@@ -13415,12 +13801,14 @@
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr">
+      <c r="K196" t="n">
+        <v>140.1</v>
+      </c>
+      <c r="L196" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr"/>
       <c r="M196" t="n">
         <v>100</v>
       </c>
@@ -13458,12 +13846,14 @@
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr">
+      <c r="K197" t="n">
+        <v>782.8</v>
+      </c>
+      <c r="L197" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr"/>
       <c r="M197" t="n">
         <v>100</v>
       </c>
@@ -13497,12 +13887,14 @@
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr">
+      <c r="K198" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="L198" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr"/>
       <c r="M198" t="n">
         <v>100</v>
       </c>
@@ -13536,12 +13928,14 @@
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr">
+      <c r="K199" t="n">
+        <v>649</v>
+      </c>
+      <c r="L199" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr"/>
       <c r="M199" t="n">
         <v>100</v>
       </c>
@@ -13575,12 +13969,14 @@
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr">
+      <c r="K200" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="L200" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr"/>
       <c r="M200" t="n">
         <v>100</v>
       </c>
@@ -13614,12 +14010,14 @@
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr">
+      <c r="K201" t="n">
+        <v>748.4</v>
+      </c>
+      <c r="L201" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr"/>
       <c r="M201" t="n">
         <v>100</v>
       </c>
@@ -13653,12 +14051,14 @@
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr">
+      <c r="K202" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="L202" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr"/>
       <c r="M202" t="n">
         <v>100</v>
       </c>
@@ -13692,12 +14092,14 @@
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr">
+      <c r="K203" t="n">
+        <v>483.7</v>
+      </c>
+      <c r="L203" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr"/>
       <c r="M203" t="n">
         <v>100</v>
       </c>
@@ -13731,12 +14133,14 @@
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr">
+      <c r="K204" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="L204" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr"/>
       <c r="M204" t="n">
         <v>100</v>
       </c>
@@ -13770,12 +14174,14 @@
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr">
+      <c r="K205" t="n">
+        <v>348</v>
+      </c>
+      <c r="L205" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr"/>
       <c r="M205" t="n">
         <v>100</v>
       </c>
@@ -13809,12 +14215,14 @@
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr">
+      <c r="K206" t="n">
+        <v>147</v>
+      </c>
+      <c r="L206" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr"/>
       <c r="M206" t="n">
         <v>100</v>
       </c>
@@ -13848,12 +14256,14 @@
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr">
+      <c r="K207" t="n">
+        <v>739.9</v>
+      </c>
+      <c r="L207" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr"/>
       <c r="M207" t="n">
         <v>100</v>
       </c>
@@ -13887,12 +14297,14 @@
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr">
+      <c r="K208" t="n">
+        <v>318.6</v>
+      </c>
+      <c r="L208" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr"/>
       <c r="M208" t="n">
         <v>100</v>
       </c>
@@ -13926,12 +14338,14 @@
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr">
+      <c r="K209" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="L209" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr"/>
       <c r="M209" t="n">
         <v>100</v>
       </c>
@@ -13965,12 +14379,14 @@
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr">
+      <c r="K210" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="L210" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr"/>
       <c r="M210" t="n">
         <v>100</v>
       </c>
@@ -14004,12 +14420,14 @@
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr">
+      <c r="K211" t="n">
+        <v>260</v>
+      </c>
+      <c r="L211" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr"/>
       <c r="M211" t="n">
         <v>100</v>
       </c>
@@ -14043,12 +14461,14 @@
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr">
+      <c r="K212" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="L212" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr"/>
       <c r="M212" t="n">
         <v>100</v>
       </c>
@@ -14082,12 +14502,14 @@
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr">
+      <c r="K213" t="n">
+        <v>260.4</v>
+      </c>
+      <c r="L213" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr"/>
       <c r="M213" t="n">
         <v>100</v>
       </c>
@@ -14121,12 +14543,14 @@
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr">
+      <c r="K214" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="L214" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr"/>
       <c r="M214" t="n">
         <v>100</v>
       </c>
@@ -14160,12 +14584,14 @@
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr">
+      <c r="K215" t="n">
+        <v>488.2</v>
+      </c>
+      <c r="L215" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr"/>
       <c r="M215" t="n">
         <v>100</v>
       </c>
@@ -14199,12 +14625,14 @@
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr">
+      <c r="K216" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="L216" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr"/>
       <c r="M216" t="n">
         <v>100</v>
       </c>
@@ -14238,12 +14666,14 @@
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr">
+      <c r="K217" t="n">
+        <v>797</v>
+      </c>
+      <c r="L217" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr"/>
       <c r="M217" t="n">
         <v>100</v>
       </c>
@@ -14277,12 +14707,14 @@
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr">
+      <c r="K218" t="n">
+        <v>387.8</v>
+      </c>
+      <c r="L218" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr"/>
       <c r="M218" t="n">
         <v>100</v>
       </c>
@@ -14316,12 +14748,14 @@
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr">
+      <c r="K219" t="n">
+        <v>575.7</v>
+      </c>
+      <c r="L219" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr"/>
       <c r="M219" t="n">
         <v>100</v>
       </c>
@@ -14359,12 +14793,14 @@
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr">
+      <c r="K220" t="n">
+        <v>193.2</v>
+      </c>
+      <c r="L220" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr"/>
       <c r="M220" t="n">
         <v>100</v>
       </c>
@@ -14402,12 +14838,14 @@
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr">
+      <c r="K221" t="n">
+        <v>611.9</v>
+      </c>
+      <c r="L221" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr"/>
       <c r="M221" t="n">
         <v>100</v>
       </c>
@@ -14441,12 +14879,14 @@
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr">
+      <c r="K222" t="n">
+        <v>204.8</v>
+      </c>
+      <c r="L222" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr"/>
       <c r="M222" t="n">
         <v>100</v>
       </c>
@@ -14480,12 +14920,14 @@
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr">
+      <c r="K223" t="n">
+        <v>495.5</v>
+      </c>
+      <c r="L223" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr"/>
       <c r="M223" t="n">
         <v>100</v>
       </c>
@@ -14519,12 +14961,14 @@
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr">
+      <c r="K224" t="n">
+        <v>228.1</v>
+      </c>
+      <c r="L224" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr"/>
       <c r="M224" t="n">
         <v>100</v>
       </c>
@@ -14558,12 +15002,14 @@
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr">
+      <c r="K225" t="n">
+        <v>635.6</v>
+      </c>
+      <c r="L225" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr"/>
       <c r="M225" t="n">
         <v>100</v>
       </c>
@@ -14597,12 +15043,14 @@
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr">
+      <c r="K226" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="L226" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr"/>
       <c r="M226" t="n">
         <v>100</v>
       </c>
@@ -14636,12 +15084,14 @@
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr">
+      <c r="K227" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="L227" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr"/>
       <c r="M227" t="n">
         <v>100</v>
       </c>
@@ -14675,12 +15125,14 @@
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr">
+      <c r="K228" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="L228" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr"/>
       <c r="M228" t="n">
         <v>100</v>
       </c>
@@ -14714,12 +15166,14 @@
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr">
+      <c r="K229" t="n">
+        <v>732.5</v>
+      </c>
+      <c r="L229" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr"/>
       <c r="M229" t="n">
         <v>100</v>
       </c>
@@ -14753,12 +15207,14 @@
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr">
+      <c r="K230" t="n">
+        <v>305.6</v>
+      </c>
+      <c r="L230" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr"/>
       <c r="M230" t="n">
         <v>100</v>
       </c>
@@ -14792,12 +15248,14 @@
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr">
+      <c r="K231" t="n">
+        <v>567.4</v>
+      </c>
+      <c r="L231" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr"/>
       <c r="M231" t="n">
         <v>100</v>
       </c>
@@ -14831,12 +15289,14 @@
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr">
+      <c r="K232" t="n">
+        <v>252</v>
+      </c>
+      <c r="L232" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr"/>
       <c r="M232" t="n">
         <v>100</v>
       </c>
@@ -14870,12 +15330,14 @@
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr">
+      <c r="K233" t="n">
+        <v>214.8</v>
+      </c>
+      <c r="L233" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr"/>
       <c r="M233" t="n">
         <v>100</v>
       </c>
@@ -14909,12 +15371,14 @@
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr">
+      <c r="K234" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="L234" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr"/>
       <c r="M234" t="n">
         <v>100</v>
       </c>
@@ -14948,12 +15412,14 @@
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr">
+      <c r="K235" t="n">
+        <v>522.3</v>
+      </c>
+      <c r="L235" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr"/>
       <c r="M235" t="n">
         <v>100</v>
       </c>
@@ -14987,12 +15453,14 @@
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr">
+      <c r="K236" t="n">
+        <v>219.3</v>
+      </c>
+      <c r="L236" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr"/>
       <c r="M236" t="n">
         <v>100</v>
       </c>
@@ -15026,12 +15494,14 @@
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr">
+      <c r="K237" t="n">
+        <v>365</v>
+      </c>
+      <c r="L237" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr"/>
       <c r="M237" t="n">
         <v>100</v>
       </c>
@@ -15065,12 +15535,14 @@
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr">
+      <c r="K238" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="L238" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr"/>
       <c r="M238" t="n">
         <v>100</v>
       </c>
@@ -15104,12 +15576,14 @@
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr">
+      <c r="K239" t="n">
+        <v>618.6</v>
+      </c>
+      <c r="L239" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr"/>
       <c r="M239" t="n">
         <v>100</v>
       </c>
@@ -15143,12 +15617,14 @@
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr">
+      <c r="K240" t="n">
+        <v>280.9</v>
+      </c>
+      <c r="L240" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr"/>
       <c r="M240" t="n">
         <v>100</v>
       </c>
@@ -15182,12 +15658,14 @@
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr">
+      <c r="K241" t="n">
+        <v>726.7</v>
+      </c>
+      <c r="L241" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr"/>
       <c r="M241" t="n">
         <v>100</v>
       </c>
@@ -15221,12 +15699,14 @@
       </c>
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr">
+      <c r="K242" t="n">
+        <v>249.3</v>
+      </c>
+      <c r="L242" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr"/>
       <c r="M242" t="n">
         <v>100</v>
       </c>
@@ -15260,12 +15740,14 @@
       </c>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr">
+      <c r="K243" t="n">
+        <v>326.9</v>
+      </c>
+      <c r="L243" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr"/>
       <c r="M243" t="n">
         <v>100</v>
       </c>
@@ -15303,12 +15785,14 @@
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr">
+      <c r="K244" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="L244" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr"/>
       <c r="M244" t="n">
         <v>100</v>
       </c>
@@ -15346,12 +15830,14 @@
       </c>
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr">
+      <c r="K245" t="n">
+        <v>403.8</v>
+      </c>
+      <c r="L245" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr"/>
       <c r="M245" t="n">
         <v>100</v>
       </c>
@@ -15385,12 +15871,14 @@
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr">
+      <c r="K246" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="L246" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr"/>
       <c r="M246" t="n">
         <v>100</v>
       </c>
@@ -15424,12 +15912,14 @@
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr">
+      <c r="K247" t="n">
+        <v>633.4</v>
+      </c>
+      <c r="L247" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr"/>
       <c r="M247" t="n">
         <v>100</v>
       </c>
@@ -15463,12 +15953,14 @@
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr">
+      <c r="K248" t="n">
+        <v>249.1</v>
+      </c>
+      <c r="L248" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr"/>
       <c r="M248" t="n">
         <v>100</v>
       </c>
@@ -15502,12 +15994,14 @@
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr">
+      <c r="K249" t="n">
+        <v>854.6</v>
+      </c>
+      <c r="L249" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr"/>
       <c r="M249" t="n">
         <v>100</v>
       </c>
@@ -15541,12 +16035,14 @@
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr">
+      <c r="K250" t="n">
+        <v>333</v>
+      </c>
+      <c r="L250" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr"/>
       <c r="M250" t="n">
         <v>100</v>
       </c>
@@ -15580,12 +16076,14 @@
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr">
+      <c r="K251" t="n">
+        <v>432.4</v>
+      </c>
+      <c r="L251" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr"/>
       <c r="M251" t="n">
         <v>100</v>
       </c>
@@ -15619,12 +16117,14 @@
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr">
+      <c r="K252" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="L252" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr"/>
       <c r="M252" t="n">
         <v>100</v>
       </c>
@@ -15658,12 +16158,14 @@
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr">
+      <c r="K253" t="n">
+        <v>454.2</v>
+      </c>
+      <c r="L253" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr"/>
       <c r="M253" t="n">
         <v>100</v>
       </c>
@@ -15697,12 +16199,14 @@
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr">
+      <c r="K254" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="L254" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr"/>
       <c r="M254" t="n">
         <v>100</v>
       </c>
@@ -15736,12 +16240,14 @@
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr">
+      <c r="K255" t="n">
+        <v>594.8</v>
+      </c>
+      <c r="L255" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr"/>
       <c r="M255" t="n">
         <v>100</v>
       </c>
@@ -15775,12 +16281,14 @@
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr">
+      <c r="K256" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="L256" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr"/>
       <c r="M256" t="n">
         <v>100</v>
       </c>
@@ -15814,12 +16322,14 @@
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr">
+      <c r="K257" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="L257" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr"/>
       <c r="M257" t="n">
         <v>100</v>
       </c>
@@ -15853,12 +16363,14 @@
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr">
+      <c r="K258" t="n">
+        <v>151</v>
+      </c>
+      <c r="L258" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr"/>
       <c r="M258" t="n">
         <v>100</v>
       </c>
@@ -15892,12 +16404,14 @@
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr">
+      <c r="K259" t="n">
+        <v>478.5</v>
+      </c>
+      <c r="L259" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr"/>
       <c r="M259" t="n">
         <v>100</v>
       </c>
@@ -15931,12 +16445,14 @@
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr">
+      <c r="K260" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="L260" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr"/>
       <c r="M260" t="n">
         <v>100</v>
       </c>
@@ -15970,12 +16486,14 @@
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr">
+      <c r="K261" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="L261" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr"/>
       <c r="M261" t="n">
         <v>100</v>
       </c>
@@ -16009,12 +16527,14 @@
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr">
+      <c r="K262" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="L262" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr"/>
       <c r="M262" t="n">
         <v>100</v>
       </c>
@@ -16048,12 +16568,14 @@
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr">
+      <c r="K263" t="n">
+        <v>319.3</v>
+      </c>
+      <c r="L263" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr"/>
       <c r="M263" t="n">
         <v>100</v>
       </c>
@@ -16087,12 +16609,14 @@
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr">
+      <c r="K264" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="L264" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr"/>
       <c r="M264" t="n">
         <v>100</v>
       </c>
@@ -16126,12 +16650,14 @@
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr">
+      <c r="K265" t="n">
+        <v>304.2</v>
+      </c>
+      <c r="L265" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr"/>
       <c r="M265" t="n">
         <v>100</v>
       </c>
@@ -16165,12 +16691,14 @@
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr">
+      <c r="K266" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="L266" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr"/>
       <c r="M266" t="n">
         <v>100</v>
       </c>
@@ -16204,12 +16732,14 @@
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr">
+      <c r="K267" t="n">
+        <v>725.9</v>
+      </c>
+      <c r="L267" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr"/>
       <c r="M267" t="n">
         <v>100</v>
       </c>
@@ -16247,12 +16777,14 @@
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr">
+      <c r="K268" t="n">
+        <v>294.1</v>
+      </c>
+      <c r="L268" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr"/>
       <c r="M268" t="n">
         <v>100</v>
       </c>
@@ -16290,12 +16822,14 @@
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr">
+      <c r="K269" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="L269" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr"/>
       <c r="M269" t="n">
         <v>100</v>
       </c>
@@ -16329,12 +16863,14 @@
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr">
+      <c r="K270" t="n">
+        <v>154.2</v>
+      </c>
+      <c r="L270" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr"/>
       <c r="M270" t="n">
         <v>100</v>
       </c>
@@ -16368,12 +16904,14 @@
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr">
+      <c r="K271" t="n">
+        <v>268</v>
+      </c>
+      <c r="L271" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr"/>
       <c r="M271" t="n">
         <v>100</v>
       </c>
@@ -16407,12 +16945,14 @@
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr">
+      <c r="K272" t="n">
+        <v>100</v>
+      </c>
+      <c r="L272" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
         <v>100</v>
       </c>
@@ -16446,12 +16986,14 @@
       </c>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr">
+      <c r="K273" t="n">
+        <v>799.8</v>
+      </c>
+      <c r="L273" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
         <v>100</v>
       </c>
@@ -16485,12 +17027,14 @@
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr">
+      <c r="K274" t="n">
+        <v>377.8</v>
+      </c>
+      <c r="L274" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
         <v>100</v>
       </c>
@@ -16524,12 +17068,14 @@
       </c>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr">
+      <c r="K275" t="n">
+        <v>901.4</v>
+      </c>
+      <c r="L275" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
         <v>100</v>
       </c>
@@ -16563,12 +17109,14 @@
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr">
+      <c r="K276" t="n">
+        <v>396</v>
+      </c>
+      <c r="L276" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
         <v>100</v>
       </c>
@@ -16602,12 +17150,14 @@
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr">
+      <c r="K277" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="L277" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
         <v>100</v>
       </c>
@@ -16641,12 +17191,14 @@
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr">
+      <c r="K278" t="n">
+        <v>177.3</v>
+      </c>
+      <c r="L278" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr"/>
       <c r="M278" t="n">
         <v>100</v>
       </c>
@@ -16680,12 +17232,14 @@
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr">
+      <c r="K279" t="n">
+        <v>278.9</v>
+      </c>
+      <c r="L279" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
         <v>100</v>
       </c>
@@ -16719,12 +17273,14 @@
       </c>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr">
+      <c r="K280" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="L280" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr"/>
       <c r="M280" t="n">
         <v>100</v>
       </c>
@@ -16758,12 +17314,14 @@
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr">
+      <c r="K281" t="n">
+        <v>210.3</v>
+      </c>
+      <c r="L281" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr"/>
       <c r="M281" t="n">
         <v>100</v>
       </c>
@@ -16797,12 +17355,14 @@
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr">
+      <c r="K282" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="L282" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr"/>
       <c r="M282" t="n">
         <v>100</v>
       </c>
@@ -16836,12 +17396,14 @@
       </c>
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr">
+      <c r="K283" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="L283" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr"/>
       <c r="M283" t="n">
         <v>100</v>
       </c>
@@ -16875,12 +17437,14 @@
       </c>
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr">
+      <c r="K284" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="L284" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr"/>
       <c r="M284" t="n">
         <v>100</v>
       </c>
@@ -16914,12 +17478,14 @@
       </c>
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr">
+      <c r="K285" t="n">
+        <v>422.4</v>
+      </c>
+      <c r="L285" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr"/>
       <c r="M285" t="n">
         <v>100</v>
       </c>
@@ -16953,12 +17519,14 @@
       </c>
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr">
+      <c r="K286" t="n">
+        <v>171</v>
+      </c>
+      <c r="L286" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr"/>
       <c r="M286" t="n">
         <v>100</v>
       </c>
@@ -16992,12 +17560,14 @@
       </c>
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr">
+      <c r="K287" t="n">
+        <v>410.6</v>
+      </c>
+      <c r="L287" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr"/>
       <c r="M287" t="n">
         <v>100</v>
       </c>
@@ -17031,12 +17601,14 @@
       </c>
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr">
+      <c r="K288" t="n">
+        <v>203</v>
+      </c>
+      <c r="L288" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr"/>
       <c r="M288" t="n">
         <v>100</v>
       </c>
@@ -17070,12 +17642,14 @@
       </c>
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr">
+      <c r="K289" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="L289" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr"/>
       <c r="M289" t="n">
         <v>100</v>
       </c>
@@ -17109,12 +17683,14 @@
       </c>
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr">
+      <c r="K290" t="n">
+        <v>140.1</v>
+      </c>
+      <c r="L290" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr"/>
       <c r="M290" t="n">
         <v>100</v>
       </c>
@@ -17148,12 +17724,14 @@
       </c>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr">
+      <c r="K291" t="n">
+        <v>693.1</v>
+      </c>
+      <c r="L291" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr"/>
       <c r="M291" t="n">
         <v>100</v>
       </c>
@@ -17191,12 +17769,14 @@
       </c>
       <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr">
+      <c r="K292" t="n">
+        <v>238</v>
+      </c>
+      <c r="L292" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr"/>
       <c r="M292" t="n">
         <v>100</v>
       </c>
@@ -17234,12 +17814,14 @@
       </c>
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr">
+      <c r="K293" t="n">
+        <v>408.7</v>
+      </c>
+      <c r="L293" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr"/>
       <c r="M293" t="n">
         <v>100</v>
       </c>
@@ -17273,12 +17855,14 @@
       </c>
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr">
+      <c r="K294" t="n">
+        <v>209.6</v>
+      </c>
+      <c r="L294" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L294" t="inlineStr"/>
       <c r="M294" t="n">
         <v>100</v>
       </c>
@@ -17312,12 +17896,14 @@
       </c>
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr">
+      <c r="K295" t="n">
+        <v>509.9</v>
+      </c>
+      <c r="L295" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr"/>
       <c r="M295" t="n">
         <v>100</v>
       </c>
@@ -17351,12 +17937,14 @@
       </c>
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr">
+      <c r="K296" t="n">
+        <v>197</v>
+      </c>
+      <c r="L296" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr"/>
       <c r="M296" t="n">
         <v>100</v>
       </c>
@@ -17390,12 +17978,14 @@
       </c>
       <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr">
+      <c r="K297" t="n">
+        <v>678</v>
+      </c>
+      <c r="L297" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr"/>
       <c r="M297" t="n">
         <v>100</v>
       </c>
@@ -17429,12 +18019,14 @@
       </c>
       <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr">
+      <c r="K298" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="L298" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr"/>
       <c r="M298" t="n">
         <v>100</v>
       </c>
@@ -17468,12 +18060,14 @@
       </c>
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr">
+      <c r="K299" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="L299" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr"/>
       <c r="M299" t="n">
         <v>100</v>
       </c>
@@ -17507,12 +18101,14 @@
       </c>
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr">
+      <c r="K300" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="L300" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr"/>
       <c r="M300" t="n">
         <v>100</v>
       </c>
@@ -17546,12 +18142,14 @@
       </c>
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr">
+      <c r="K301" t="n">
+        <v>712.2</v>
+      </c>
+      <c r="L301" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr"/>
       <c r="M301" t="n">
         <v>100</v>
       </c>
@@ -17585,12 +18183,14 @@
       </c>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr">
+      <c r="K302" t="n">
+        <v>247.3</v>
+      </c>
+      <c r="L302" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr"/>
       <c r="M302" t="n">
         <v>100</v>
       </c>
@@ -17624,12 +18224,14 @@
       </c>
       <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr"/>
-      <c r="K303" t="inlineStr">
+      <c r="K303" t="n">
+        <v>762.6</v>
+      </c>
+      <c r="L303" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr"/>
       <c r="M303" t="n">
         <v>100</v>
       </c>
@@ -17663,12 +18265,14 @@
       </c>
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr">
+      <c r="K304" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="L304" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr"/>
       <c r="M304" t="n">
         <v>100</v>
       </c>
@@ -17702,12 +18306,14 @@
       </c>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr">
+      <c r="K305" t="n">
+        <v>541</v>
+      </c>
+      <c r="L305" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr"/>
       <c r="M305" t="n">
         <v>100</v>
       </c>
@@ -17741,12 +18347,14 @@
       </c>
       <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr"/>
-      <c r="K306" t="inlineStr">
+      <c r="K306" t="n">
+        <v>228.6</v>
+      </c>
+      <c r="L306" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr"/>
       <c r="M306" t="n">
         <v>100</v>
       </c>
@@ -17780,12 +18388,14 @@
       </c>
       <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr"/>
-      <c r="K307" t="inlineStr">
+      <c r="K307" t="n">
+        <v>250.3</v>
+      </c>
+      <c r="L307" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr"/>
       <c r="M307" t="n">
         <v>100</v>
       </c>
@@ -17819,12 +18429,14 @@
       </c>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr">
+      <c r="K308" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="L308" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr"/>
       <c r="M308" t="n">
         <v>100</v>
       </c>
@@ -17858,12 +18470,14 @@
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr">
+      <c r="K309" t="n">
+        <v>524.1</v>
+      </c>
+      <c r="L309" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr"/>
       <c r="M309" t="n">
         <v>100</v>
       </c>
@@ -17897,12 +18511,14 @@
       </c>
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr"/>
-      <c r="K310" t="inlineStr">
+      <c r="K310" t="n">
+        <v>202.8</v>
+      </c>
+      <c r="L310" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr"/>
       <c r="M310" t="n">
         <v>100</v>
       </c>
@@ -17936,12 +18552,14 @@
       </c>
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr">
+      <c r="K311" t="n">
+        <v>705</v>
+      </c>
+      <c r="L311" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr"/>
       <c r="M311" t="n">
         <v>100</v>
       </c>
@@ -17975,12 +18593,14 @@
       </c>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr">
+      <c r="K312" t="n">
+        <v>323.9</v>
+      </c>
+      <c r="L312" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr"/>
       <c r="M312" t="n">
         <v>100</v>
       </c>
@@ -18014,12 +18634,14 @@
       </c>
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr">
+      <c r="K313" t="n">
+        <v>766.3</v>
+      </c>
+      <c r="L313" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr"/>
       <c r="M313" t="n">
         <v>100</v>
       </c>
@@ -18053,12 +18675,14 @@
       </c>
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr">
+      <c r="K314" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="L314" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr"/>
       <c r="M314" t="n">
         <v>100</v>
       </c>
@@ -18092,12 +18716,14 @@
       </c>
       <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr">
+      <c r="K315" t="n">
+        <v>748.3</v>
+      </c>
+      <c r="L315" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr"/>
       <c r="M315" t="n">
         <v>100</v>
       </c>
@@ -18135,12 +18761,14 @@
       </c>
       <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr">
+      <c r="K316" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="L316" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr"/>
       <c r="M316" t="n">
         <v>100</v>
       </c>
@@ -18178,12 +18806,14 @@
       </c>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr">
+      <c r="K317" t="n">
+        <v>698.2</v>
+      </c>
+      <c r="L317" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr"/>
       <c r="M317" t="n">
         <v>100</v>
       </c>
@@ -18217,12 +18847,14 @@
       </c>
       <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr"/>
-      <c r="K318" t="inlineStr">
+      <c r="K318" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="L318" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr"/>
       <c r="M318" t="n">
         <v>100</v>
       </c>
@@ -18256,12 +18888,14 @@
       </c>
       <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr">
+      <c r="K319" t="n">
+        <v>629</v>
+      </c>
+      <c r="L319" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr"/>
       <c r="M319" t="n">
         <v>100</v>
       </c>
@@ -18295,12 +18929,14 @@
       </c>
       <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr">
+      <c r="K320" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="L320" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr"/>
       <c r="M320" t="n">
         <v>100</v>
       </c>
@@ -18334,12 +18970,14 @@
       </c>
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr">
+      <c r="K321" t="n">
+        <v>273.1</v>
+      </c>
+      <c r="L321" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr"/>
       <c r="M321" t="n">
         <v>100</v>
       </c>
@@ -18373,12 +19011,14 @@
       </c>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr">
+      <c r="K322" t="n">
+        <v>135</v>
+      </c>
+      <c r="L322" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr"/>
       <c r="M322" t="n">
         <v>100</v>
       </c>
@@ -18412,12 +19052,14 @@
       </c>
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr">
+      <c r="K323" t="n">
+        <v>741</v>
+      </c>
+      <c r="L323" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr"/>
       <c r="M323" t="n">
         <v>100</v>
       </c>
@@ -18451,12 +19093,14 @@
       </c>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr">
+      <c r="K324" t="n">
+        <v>277.4</v>
+      </c>
+      <c r="L324" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr"/>
       <c r="M324" t="n">
         <v>100</v>
       </c>
@@ -18490,12 +19134,14 @@
       </c>
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr"/>
-      <c r="K325" t="inlineStr">
+      <c r="K325" t="n">
+        <v>428.9</v>
+      </c>
+      <c r="L325" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr"/>
       <c r="M325" t="n">
         <v>100</v>
       </c>
@@ -18529,12 +19175,14 @@
       </c>
       <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr">
+      <c r="K326" t="n">
+        <v>165</v>
+      </c>
+      <c r="L326" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr"/>
       <c r="M326" t="n">
         <v>100</v>
       </c>
@@ -18568,12 +19216,14 @@
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr">
+      <c r="K327" t="n">
+        <v>255.7</v>
+      </c>
+      <c r="L327" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr"/>
       <c r="M327" t="n">
         <v>100</v>
       </c>
@@ -18607,12 +19257,14 @@
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr">
+      <c r="K328" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="L328" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L328" t="inlineStr"/>
       <c r="M328" t="n">
         <v>100</v>
       </c>
@@ -18646,12 +19298,14 @@
       </c>
       <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr">
+      <c r="K329" t="n">
+        <v>426.8</v>
+      </c>
+      <c r="L329" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr"/>
       <c r="M329" t="n">
         <v>100</v>
       </c>
@@ -18685,12 +19339,14 @@
       </c>
       <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr">
+      <c r="K330" t="n">
+        <v>152</v>
+      </c>
+      <c r="L330" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr"/>
       <c r="M330" t="n">
         <v>100</v>
       </c>
@@ -18724,12 +19380,14 @@
       </c>
       <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr">
+      <c r="K331" t="n">
+        <v>643</v>
+      </c>
+      <c r="L331" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr"/>
       <c r="M331" t="n">
         <v>100</v>
       </c>
@@ -18763,12 +19421,14 @@
       </c>
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr">
+      <c r="K332" t="n">
+        <v>304</v>
+      </c>
+      <c r="L332" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr"/>
       <c r="M332" t="n">
         <v>100</v>
       </c>
@@ -18802,12 +19462,14 @@
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr">
+      <c r="K333" t="n">
+        <v>673.4</v>
+      </c>
+      <c r="L333" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr"/>
       <c r="M333" t="n">
         <v>100</v>
       </c>
@@ -18841,12 +19503,14 @@
       </c>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr">
+      <c r="K334" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="L334" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr"/>
       <c r="M334" t="n">
         <v>100</v>
       </c>
@@ -18880,12 +19544,14 @@
       </c>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr">
+      <c r="K335" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="L335" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr"/>
       <c r="M335" t="n">
         <v>100</v>
       </c>
@@ -18919,12 +19585,14 @@
       </c>
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr">
+      <c r="K336" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="L336" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr"/>
       <c r="M336" t="n">
         <v>100</v>
       </c>
@@ -18958,12 +19626,14 @@
       </c>
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr">
+      <c r="K337" t="n">
+        <v>835.1</v>
+      </c>
+      <c r="L337" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L337" t="inlineStr"/>
       <c r="M337" t="n">
         <v>100</v>
       </c>
@@ -18997,12 +19667,14 @@
       </c>
       <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr"/>
-      <c r="K338" t="inlineStr">
+      <c r="K338" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="L338" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L338" t="inlineStr"/>
       <c r="M338" t="n">
         <v>100</v>
       </c>
@@ -19036,12 +19708,14 @@
       </c>
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr">
+      <c r="K339" t="n">
+        <v>872.4</v>
+      </c>
+      <c r="L339" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L339" t="inlineStr"/>
       <c r="M339" t="n">
         <v>100</v>
       </c>
@@ -19079,12 +19753,14 @@
       </c>
       <c r="I340" t="inlineStr"/>
       <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr">
+      <c r="K340" t="n">
+        <v>408.2</v>
+      </c>
+      <c r="L340" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L340" t="inlineStr"/>
       <c r="M340" t="n">
         <v>100</v>
       </c>
@@ -19122,12 +19798,14 @@
       </c>
       <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr">
+      <c r="K341" t="n">
+        <v>514.6</v>
+      </c>
+      <c r="L341" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L341" t="inlineStr"/>
       <c r="M341" t="n">
         <v>100</v>
       </c>
@@ -19161,12 +19839,14 @@
       </c>
       <c r="I342" t="inlineStr"/>
       <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr">
+      <c r="K342" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="L342" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr"/>
       <c r="M342" t="n">
         <v>100</v>
       </c>
@@ -19200,12 +19880,14 @@
       </c>
       <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr">
+      <c r="K343" t="n">
+        <v>699.4</v>
+      </c>
+      <c r="L343" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr"/>
       <c r="M343" t="n">
         <v>100</v>
       </c>
@@ -19239,12 +19921,14 @@
       </c>
       <c r="I344" t="inlineStr"/>
       <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr">
+      <c r="K344" t="n">
+        <v>284.7</v>
+      </c>
+      <c r="L344" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr"/>
       <c r="M344" t="n">
         <v>100</v>
       </c>
@@ -19278,12 +19962,14 @@
       </c>
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr">
+      <c r="K345" t="n">
+        <v>247.1</v>
+      </c>
+      <c r="L345" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L345" t="inlineStr"/>
       <c r="M345" t="n">
         <v>100</v>
       </c>
@@ -19317,12 +20003,14 @@
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr">
+      <c r="K346" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="L346" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L346" t="inlineStr"/>
       <c r="M346" t="n">
         <v>100</v>
       </c>
@@ -19356,12 +20044,14 @@
       </c>
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr">
+      <c r="K347" t="n">
+        <v>447.9</v>
+      </c>
+      <c r="L347" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L347" t="inlineStr"/>
       <c r="M347" t="n">
         <v>100</v>
       </c>
@@ -19395,12 +20085,14 @@
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr">
+      <c r="K348" t="n">
+        <v>201.2</v>
+      </c>
+      <c r="L348" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L348" t="inlineStr"/>
       <c r="M348" t="n">
         <v>100</v>
       </c>
@@ -19434,12 +20126,14 @@
       </c>
       <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr">
+      <c r="K349" t="n">
+        <v>264.1</v>
+      </c>
+      <c r="L349" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr"/>
       <c r="M349" t="n">
         <v>100</v>
       </c>
@@ -19473,12 +20167,14 @@
       </c>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr">
+      <c r="K350" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="L350" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr"/>
       <c r="M350" t="n">
         <v>100</v>
       </c>
@@ -19512,12 +20208,14 @@
       </c>
       <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr">
+      <c r="K351" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="L351" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr"/>
       <c r="M351" t="n">
         <v>100</v>
       </c>
@@ -19551,12 +20249,14 @@
       </c>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr">
+      <c r="K352" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="L352" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr"/>
       <c r="M352" t="n">
         <v>100</v>
       </c>
@@ -19590,12 +20290,14 @@
       </c>
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr">
+      <c r="K353" t="n">
+        <v>792.9</v>
+      </c>
+      <c r="L353" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr"/>
       <c r="M353" t="n">
         <v>100</v>
       </c>
@@ -19629,12 +20331,14 @@
       </c>
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr"/>
-      <c r="K354" t="inlineStr">
+      <c r="K354" t="n">
+        <v>405.2</v>
+      </c>
+      <c r="L354" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L354" t="inlineStr"/>
       <c r="M354" t="n">
         <v>100</v>
       </c>
@@ -19668,12 +20372,14 @@
       </c>
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr">
+      <c r="K355" t="n">
+        <v>792.6</v>
+      </c>
+      <c r="L355" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr"/>
       <c r="M355" t="n">
         <v>100</v>
       </c>
@@ -19707,12 +20413,14 @@
       </c>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr">
+      <c r="K356" t="n">
+        <v>425.3</v>
+      </c>
+      <c r="L356" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr"/>
       <c r="M356" t="n">
         <v>100</v>
       </c>
@@ -19746,12 +20454,14 @@
       </c>
       <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr"/>
-      <c r="K357" t="inlineStr">
+      <c r="K357" t="n">
+        <v>222.7</v>
+      </c>
+      <c r="L357" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L357" t="inlineStr"/>
       <c r="M357" t="n">
         <v>100</v>
       </c>
@@ -19785,12 +20495,14 @@
       </c>
       <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr"/>
-      <c r="K358" t="inlineStr">
+      <c r="K358" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="L358" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr"/>
       <c r="M358" t="n">
         <v>100</v>
       </c>
@@ -19824,12 +20536,14 @@
       </c>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr">
+      <c r="K359" t="n">
+        <v>799.1</v>
+      </c>
+      <c r="L359" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L359" t="inlineStr"/>
       <c r="M359" t="n">
         <v>100</v>
       </c>
@@ -19863,12 +20577,14 @@
       </c>
       <c r="I360" t="inlineStr"/>
       <c r="J360" t="inlineStr"/>
-      <c r="K360" t="inlineStr">
+      <c r="K360" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="L360" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr"/>
       <c r="M360" t="n">
         <v>100</v>
       </c>
@@ -19902,12 +20618,14 @@
       </c>
       <c r="I361" t="inlineStr"/>
       <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr">
+      <c r="K361" t="n">
+        <v>243.2</v>
+      </c>
+      <c r="L361" t="inlineStr">
         <is>
           <t>가공</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr"/>
       <c r="M361" t="n">
         <v>100</v>
       </c>
@@ -19941,12 +20659,14 @@
       </c>
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr"/>
-      <c r="K362" t="inlineStr">
+      <c r="K362" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="L362" t="inlineStr">
         <is>
           <t>핸들링</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr"/>
       <c r="M362" t="n">
         <v>100</v>
       </c>

--- a/factory-twin/data/sample_filled_template.xlsx
+++ b/factory-twin/data/sample_filled_template.xlsx
@@ -914,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -962,152 +962,159 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【필수】 당일 투입 현장 수 / 당일 출하 현장 수 (처리량 검증: 출하 = 투입 − ΔWIP)</t>
+          <t>【필수】 앞으로 2주(로깅 기간)가 평소보다 한가한가 바쁜가? 재공이 쌓이는 날이 3~4일은 있는가? (한가한 2주는 구조 검증에 무가치 — 연구 18)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>실측 → 도면 → 재단표 작성까지 보통 며칠? 누가? 도면 대기 건수?</t>
+          <t>【필수】 당일 투입 현장 수 / 당일 출하 현장 수 (처리량 검증: 출하 = 투입 − ΔWIP)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>탑차 수, 시공팀 수, 하루 시공 가능 현장 수, 상차 시간</t>
+          <t>실측 → 도면 → 재단표 작성까지 보통 며칠? 누가? 도면 대기 건수?</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>시공일이 바뀌거나 취소되는 일이 한 달에 몇 번? 현장에서 불량 발견해 급히 재제작하는 일은?</t>
+          <t>탑차 수, 시공팀 수, 하루 시공 가능 현장 수, 상차 시간</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>주력 제품군과 월 생산량</t>
+          <t>시공일이 바뀌거나 취소되는 일이 한 달에 몇 번? 현장에서 불량 발견해 급히 재제작하는 일은?</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>주문 방식(수주/재고), 평균 리드타임</t>
+          <t>주력 제품군과 월 생산량</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>공정 순서와 병목(왜)</t>
+          <t>주문 방식(수주/재고), 평균 리드타임</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>기계별 하루 가동시간/잔업/특근</t>
+          <t>공정 순서와 병목(왜)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>가장 자주 바뀌는 세팅과 교체 시간</t>
+          <t>기계별 하루 가동시간/잔업/특근</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WIP 적치 위치와 대차/랙 수</t>
+          <t>가장 자주 바뀌는 세팅과 교체 시간</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>지게차/대차 대수, 경로, 하루 이동 횟수</t>
+          <t>WIP 적치 위치와 대차/랙 수</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>불량/재작업 비율과 원인</t>
+          <t>지게차/대차 대수, 경로, 하루 이동 횟수</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>집진기/컴프레서 가동 패턴</t>
+          <t>불량/재작업 비율과 원인</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>월 전기요금, 계약전력, 피크</t>
+          <t>집진기/컴프레서 가동 패턴</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ERP/MES/엑셀 기록 형식</t>
+          <t>월 전기요금, 계약전력, 피크</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>안전/촬영 금지 구역</t>
+          <t>ERP/MES/엑셀 기록 형식</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>향후 설비/레이아웃 변경 계획</t>
+          <t>안전/촬영 금지 구역</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>작업자 수, 숙련 구분, 외국인 비율</t>
+          <t>향후 설비/레이아웃 변경 계획</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>올해 가장 비쌌던 비용</t>
+          <t>작업자 수, 숙련 구분, 외국인 비율</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>납기 지연 횟수와 손해</t>
+          <t>올해 가장 비쌌던 비용</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>사고 싶은 기계와 망설이는 이유</t>
+          <t>납기 지연 횟수와 손해</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
+        <is>
+          <t>사고 싶은 기계와 망설이는 이유</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>정부 스마트공장 사업 수혜 이력</t>
         </is>
@@ -1124,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1141,6 +1148,9 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1213,10 +1223,25 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>부품 수(입/출)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>함께 처리한 배치(같은 원판·셋업)</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>외주 반출/반입 시각</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
           <t>사진 파일</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1391,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1400,6 +1425,10 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1417,25 +1446,45 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>만약 (조건)</t>
+          <t>트리거(언제 결정: 아침 계획/대기열 변화/카트 참/전화)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>만약 (조건 변수·비교값)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>그러면 (행동)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>우선순위(1=최상위 예외, 큰 수=평상시)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>말한 사람</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>근거 사례(주문ID·날짜)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>기록 지지(rule_fit: n/N)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>모델 반영(규칙 코드)</t>
         </is>
@@ -1449,25 +1498,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>아침 계획</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>시공일이 정해지면</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>시공일 근무일 기준 D-3 아침에 재단 투입</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>급한 건은 당일</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>반장</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>P_DESK 9/14</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1477,21 +1540,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>대기열 변화</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>같은 날 같은 색상·두께 주문이 여럿이면</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>색상·두께로 묶어 재단 후 현장별 분류</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>반장</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20947,7 +21020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20960,6 +21033,8 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21016,6 +21091,16 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>배치 규칙(고정/순환/응원·어디로)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>근속 3개월 미만(Y)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
